--- a/validCodes/validCodes_existenciasOptex.xlsx.xlsx
+++ b/validCodes/validCodes_existenciasOptex.xlsx.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B227"/>
+  <dimension ref="A1:B258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,62 +448,62 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>108</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>52590</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -515,19 +515,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>50212</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>16837</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,391 +539,391 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>52590</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17094</t>
+          <t>16840</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>18149</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>50212</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>14687</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>17094</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16034</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17500</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16833</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>17093</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -947,36 +947,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1007,7 +1007,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>14505</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1043,36 +1043,36 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>16834</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1103,36 +1103,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>19257</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20530</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>15942</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1247,55 +1247,55 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>54209</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>16423</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>18156</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1391,55 +1391,55 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>54209</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>18159</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>15356</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1535,7 +1535,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>14688</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1643,127 +1643,127 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>15421</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>19563</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>15364</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -1775,7 +1775,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -1787,7 +1787,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>50953</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>15934</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>17411</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -1871,7 +1871,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>54481</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -1919,7 +1919,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -1943,175 +1943,175 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>50952</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>19988</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>19560</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>19989</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>54481</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>18331</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>18483</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>18154</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2135,7 +2135,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>50954</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2171,7 +2171,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>51635</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2183,7 +2183,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>51635</t>
+          <t>50954</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2207,7 +2207,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>17491</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2219,7 +2219,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2231,7 +2231,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>19560</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2267,7 +2267,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2291,7 +2291,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2303,7 +2303,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2315,7 +2315,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2327,271 +2327,271 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>17492</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>51681</t>
+          <t>14459</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>51685</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>50952</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>18331</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>16403</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>51400</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>15386</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>19241</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>15374</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>18948</t>
+          <t>17095</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>13075</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>17091</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -2603,7 +2603,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -2615,7 +2615,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -2627,7 +2627,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -2687,7 +2687,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>20149</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -2711,7 +2711,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -2723,7 +2723,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>19638</t>
+          <t>19387</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>20303</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -2759,7 +2759,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -2771,7 +2771,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>15933</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -2783,7 +2783,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>15924</t>
+          <t>19128</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -2795,7 +2795,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -2807,7 +2807,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -2819,7 +2819,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -2855,7 +2855,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>16398</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -2867,7 +2867,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -2879,7 +2879,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -2891,7 +2891,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -2903,7 +2903,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>18802</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -2915,7 +2915,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>15702</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -2927,7 +2927,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>19663</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -2951,7 +2951,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -2963,7 +2963,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>13980</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>18742</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -2987,7 +2987,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3011,7 +3011,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3059,7 +3059,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>53102</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>53103</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>50827</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3107,7 +3107,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3131,18 +3131,390 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>19245</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>16398</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>18139</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>15795</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>17755</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>15729</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>16406</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>17726</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>51681</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>15702</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>15297</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>12167</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>51400</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>51685</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>17507</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>15515</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>15505</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>53102</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>13996</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>13980</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>17183</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>17125</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>16831</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>17113</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>50988</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>17109</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>15385</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
           <t>12115</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr"/>
-      <c r="B227" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>13880</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>5692</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
